--- a/Result/profitability/5455.xlsx
+++ b/Result/profitability/5455.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.84375</v>
+        <v>0.83375</v>
       </c>
       <c r="N2" t="n">
-        <v>29.555</v>
+        <v>25.4975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.16</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01875</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>22.605</v>
+        <v>26.94</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5825</v>
+        <v>0.53875</v>
       </c>
       <c r="N4" t="n">
-        <v>24.24375</v>
+        <v>29.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.56875</v>
+        <v>0.07875</v>
       </c>
       <c r="N5" t="n">
-        <v>25.91875</v>
+        <v>29.46375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.64</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08624999999999999</v>
+        <v>-0.115</v>
       </c>
       <c r="N6" t="n">
-        <v>11.62875</v>
+        <v>16.885</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.95</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.19375</v>
+        <v>-0.225</v>
       </c>
       <c r="N7" t="n">
-        <v>10.44375</v>
+        <v>13.55875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3375</v>
+        <v>-0.35875</v>
       </c>
       <c r="N8" t="n">
-        <v>7.326249999999999</v>
+        <v>9.172499999999998</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>-0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.425</v>
+        <v>-0.4249999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>2.212499999999999</v>
+        <v>2.2125</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.49375</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7812499999999991</v>
+        <v>0.78125</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.69875</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6875000000000009</v>
+        <v>-0.6875</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.72375</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.813750000000002</v>
+        <v>-1.81375</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.74375</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.305000000000001</v>
+        <v>-2.305</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5455</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1032.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.76875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.03375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4051014810751508</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.088888888888889</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.240052470485352</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
